--- a/content/CO0010/CO0010 - definition.xlsx
+++ b/content/CO0010/CO0010 - definition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>Screen type</t>
   </si>
@@ -87,14 +87,29 @@
     <t>\CO0001 - FC E-blocks CPD course\media\Digital techniques mapping.xlsx</t>
   </si>
   <si>
+    <t>Simple Suspension Bridge ST1111</t>
+  </si>
+  <si>
+    <t>Understanding Bridge Loading</t>
+  </si>
+  <si>
     <t>https://youtu.be/_5ArxUjvns4?si=d-N6CUZEIZB-Pfuc</t>
+  </si>
+  <si>
+    <t>ST1111 - Simple Suspension Bridge</t>
+  </si>
+  <si>
+    <t>All worksheets</t>
+  </si>
+  <si>
+    <t>CP9503 - Simple Suspension Bridge.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -115,6 +130,11 @@
       <name val="Arial"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <color rgb="FF0000FF"/>
     </font>
@@ -133,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -146,6 +166,9 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -469,11 +492,39 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="E8" s="5" t="s">
+      <c r="A8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="D8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1"/>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
     <row r="10" ht="15.75" customHeight="1"/>
     <row r="11" ht="15.75" customHeight="1"/>
     <row r="12" ht="15.75" customHeight="1"/>

--- a/content/CO0010/CO0010 - definition.xlsx
+++ b/content/CO0010/CO0010 - definition.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="NSPK9aTzlBsl5TFbp343W69vBmrTowIzIaydbYZaNjM="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Q4g0zQCITkdbJIZinQdTgGix8zHkCwVCm0HO98wbBkQ="/>
     </ext>
   </extLst>
 </workbook>
@@ -1515,7 +1515,6 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="E4"/>

--- a/content/CO0010/CO0010 - definition.xlsx
+++ b/content/CO0010/CO0010 - definition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>Screen type</t>
   </si>
@@ -525,7 +525,11 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1"/>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
     <row r="11" ht="15.75" customHeight="1"/>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="13" ht="15.75" customHeight="1"/>

--- a/content/CO0010/CO0010 - definition.xlsx
+++ b/content/CO0010/CO0010 - definition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
   <si>
     <t>Screen type</t>
   </si>
@@ -85,6 +85,12 @@
   </si>
   <si>
     <t>\CO0001 - FC E-blocks CPD course\media\Digital techniques mapping.xlsx</t>
+  </si>
+  <si>
+    <t>About the Author</t>
+  </si>
+  <si>
+    <t>Author.docx</t>
   </si>
   <si>
     <t>Simple Suspension Bridge ST1111</t>
@@ -384,7 +390,10 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
+    <col customWidth="1" min="1" max="2" width="12.63"/>
+    <col customWidth="1" min="3" max="3" width="27.63"/>
+    <col customWidth="1" min="4" max="4" width="28.0"/>
+    <col customWidth="1" min="5" max="6" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -493,41 +502,50 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B8" s="5">
         <v>0.1</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B9" s="5">
-        <v>4.0</v>
+        <v>0.1</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>14</v>
+      </c>
+      <c r="B10" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1"/>
@@ -1522,7 +1540,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="E4"/>
-    <hyperlink r:id="rId2" ref="E8"/>
+    <hyperlink r:id="rId2" ref="E9"/>
   </hyperlinks>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/content/CO0010/CO0010 - definition.xlsx
+++ b/content/CO0010/CO0010 - definition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>Screen type</t>
   </si>
@@ -548,7 +548,17 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1"/>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1"/>

--- a/content/CO0010/CO0010 - definition.xlsx
+++ b/content/CO0010/CO0010 - definition.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Q4g0zQCITkdbJIZinQdTgGix8zHkCwVCm0HO98wbBkQ="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="G+Q2I+46F1bwe4oyXqFPMrWIkCr/YM8UD3xfVRAqXsQ="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>Screen type</t>
   </si>
@@ -42,13 +42,13 @@
     <t>opening.png</t>
   </si>
   <si>
-    <t>HTML</t>
-  </si>
-  <si>
-    <t>Welcome</t>
-  </si>
-  <si>
-    <t>welcome.html</t>
+    <t>Document</t>
+  </si>
+  <si>
+    <t>About the Author</t>
+  </si>
+  <si>
+    <t>Author.docx</t>
   </si>
   <si>
     <t>YouTube</t>
@@ -57,40 +57,10 @@
     <t>Intro video</t>
   </si>
   <si>
-    <t>https://youtu.be/REPLACE_WITH_YOUR_VIDEO</t>
-  </si>
-  <si>
-    <t>Document</t>
-  </si>
-  <si>
-    <t>Worksheet 1</t>
-  </si>
-  <si>
-    <t>worksheet1.docx</t>
-  </si>
-  <si>
-    <t>Finished</t>
-  </si>
-  <si>
-    <t>complete.html</t>
-  </si>
-  <si>
-    <t>Sheet</t>
-  </si>
-  <si>
-    <t>Flowcode / E-blocks3</t>
-  </si>
-  <si>
-    <t>Digital Techniques mapping spreadsheet</t>
-  </si>
-  <si>
-    <t>\CO0001 - FC E-blocks CPD course\media\Digital techniques mapping.xlsx</t>
-  </si>
-  <si>
-    <t>About the Author</t>
-  </si>
-  <si>
-    <t>Author.docx</t>
+    <t>Introduction to Structures</t>
+  </si>
+  <si>
+    <t>https://youtu.be/y_pdy7oJNS8?si=-JAhAtCqQAGCLRmn</t>
   </si>
   <si>
     <t>Simple Suspension Bridge ST1111</t>
@@ -115,7 +85,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -124,15 +94,6 @@
     </font>
     <font>
       <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -159,22 +120,15 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -414,151 +368,89 @@
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>0.0</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="B3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="B4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>13</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>16</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="B6" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="D6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="15.75" customHeight="1"/>
+    <row r="9" ht="15.75" customHeight="1"/>
+    <row r="10" ht="15.75" customHeight="1"/>
+    <row r="11" ht="15.75" customHeight="1"/>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1"/>
@@ -1541,16 +1433,10 @@
     <row r="991" ht="15.75" customHeight="1"/>
     <row r="992" ht="15.75" customHeight="1"/>
     <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="E4"/>
-    <hyperlink r:id="rId2" ref="E9"/>
+    <hyperlink r:id="rId2" ref="E5"/>
   </hyperlinks>
   <drawing r:id="rId3"/>
 </worksheet>
